--- a/data/gravel/Look 765 Gravel 2025.xlsx
+++ b/data/gravel/Look 765 Gravel 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C1C76A-B454-AC46-A8D0-49E51614977D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D0D28D-6928-D44F-8B3C-9FE28578685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31420" yWindow="-24140" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,9 +272,6 @@
     <t>765 Gravel</t>
   </si>
   <si>
-    <t>https://www.lookcycle.com/us-en/products/gravel/gravel-bikes</t>
-  </si>
-  <si>
     <t>gravel</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>a8:g32</t>
+  </si>
+  <si>
+    <t>https://www.lookcycle.com/us-en/765-gravel?srsltid=AfmBOopMy3jtTr2nWShHsDnWsCDZCWSn0vBw51k8m73-xMB4gGhtDZr5</t>
   </si>
 </sst>
 </file>
@@ -349,7 +349,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -452,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,8 +468,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,12 +813,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -825,7 +826,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -834,19 +835,19 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>88</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="7"/>
@@ -941,7 +942,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="12">
         <v>70.3</v>
@@ -977,7 +978,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2">
         <v>74</v>
@@ -1013,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2">
         <v>450</v>
@@ -1049,7 +1050,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="12">
         <v>507</v>
@@ -1085,7 +1086,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="2">
         <v>577</v>
@@ -1121,7 +1122,7 @@
         <v>71</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="12">
         <v>72</v>
@@ -1157,7 +1158,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="12">
         <v>50</v>
@@ -1193,7 +1194,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="12">
         <v>420</v>
@@ -1229,7 +1230,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="12">
         <v>111.5</v>
@@ -1266,7 +1267,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="12">
         <v>395</v>
@@ -1303,7 +1304,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="8">
         <v>70</v>
@@ -1335,7 +1336,7 @@
     </row>
     <row r="22" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>72</v>
@@ -1370,9 +1371,29 @@
     </row>
     <row r="23" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="9"/>
+      <c r="C23" s="17">
+        <f>SQRT(C18^2-C21^2)+SQRT(C15^2-C21^2)</f>
+        <v>986.86374488665092</v>
+      </c>
+      <c r="D23" s="17">
+        <f t="shared" ref="D23:G23" si="0">SQRT(D18^2-D21^2)+SQRT(D15^2-D21^2)</f>
+        <v>1005.4970839611235</v>
+      </c>
+      <c r="E23" s="17">
+        <f t="shared" si="0"/>
+        <v>1024.1223061196372</v>
+      </c>
+      <c r="F23" s="17">
+        <f t="shared" si="0"/>
+        <v>1042.7401328509809</v>
+      </c>
+      <c r="G23" s="17">
+        <f t="shared" si="0"/>
+        <v>1061.3512023569465</v>
+      </c>
       <c r="H23" s="13"/>
       <c r="I23" s="7"/>
       <c r="J23" s="8"/>
@@ -1391,7 +1412,6 @@
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -1572,7 +1592,7 @@
         <v>66</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -1588,7 +1608,7 @@
         <v>69</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -1596,7 +1616,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -1666,7 +1686,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1810,7 +1830,7 @@
         <v>76</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Look 765 Gravel 2025.xlsx
+++ b/data/gravel/Look 765 Gravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D0D28D-6928-D44F-8B3C-9FE28578685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D975A7-7AB5-4F4F-9AE2-35F2AAC43CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31420" yWindow="-24140" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,24 @@
   </si>
   <si>
     <t>https://www.lookcycle.com/us-en/765-gravel?srsltid=AfmBOopMy3jtTr2nWShHsDnWsCDZCWSn0vBw51k8m73-xMB4gGhtDZr5</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -767,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1683,153 +1701,183 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="2">
-        <v>27.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57" s="2">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="2">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B68" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B69" s="2">
-        <v>3500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B70" s="2">
-        <v>4000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B79" s="16" t="s">
         <v>100</v>
       </c>
     </row>
